--- a/oPool_display/experimental_data/validation/BLI/oPool_binding_validation/oPool_validation_sample_names.xlsx
+++ b/oPool_display/experimental_data/validation/BLI/oPool_binding_validation/oPool_validation_sample_names.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/owenouyang/Desktop/Git_Repo/oPool_display/oPool_display/experimental_data/validation/BLI/oPool_binding_validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B5C538-C210-B648-B897-82483C069344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E106B239-1404-C84E-AEFA-296633B5C222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="35800" yWindow="500" windowWidth="28040" windowHeight="17440" xr2:uid="{AA0690F2-11C0-B342-945D-36AF2DF8266B}"/>
   </bookViews>
@@ -200,12 +200,6 @@
     <t>experimental_data/validation/BLI/oPool_binding_validation/A7_3.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_binding_validation/A2_6.xls</t>
-  </si>
-  <si>
-    <t>experimental_data/validation/BLI/oPool_binding_validation/A3_5.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_binding_validation/A7_8.xls</t>
   </si>
   <si>
@@ -425,12 +419,6 @@
     <t>experimental_data/validation/BLI/oPool_binding_validation/B7_3.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_binding_validation/B2_6.xls</t>
-  </si>
-  <si>
-    <t>experimental_data/validation/BLI/oPool_binding_validation/B3_5.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_binding_validation/B7_8.xls</t>
   </si>
   <si>
@@ -500,12 +488,6 @@
     <t>experimental_data/validation/BLI/oPool_binding_validation/C7_3.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_binding_validation/C2_6.xls</t>
-  </si>
-  <si>
-    <t>experimental_data/validation/BLI/oPool_binding_validation/C3_5.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_binding_validation/C7_8.xls</t>
   </si>
   <si>
@@ -650,12 +632,6 @@
     <t>experimental_data/validation/BLI/oPool_binding_validation/D7_3.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_binding_validation/E2_6.xls</t>
-  </si>
-  <si>
-    <t>experimental_data/validation/BLI/oPool_binding_validation/D3_5.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_binding_validation/D7_8.xls</t>
   </si>
   <si>
@@ -725,12 +701,6 @@
     <t>experimental_data/validation/BLI/oPool_binding_validation/E7_3.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_binding_validation/F2_6.xls</t>
-  </si>
-  <si>
-    <t>experimental_data/validation/BLI/oPool_binding_validation/E3_5.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_binding_validation/E7_8.xls</t>
   </si>
   <si>
@@ -800,12 +770,6 @@
     <t>experimental_data/validation/BLI/oPool_binding_validation/F7_3.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_binding_validation/G2_6.xls</t>
-  </si>
-  <si>
-    <t>experimental_data/validation/BLI/oPool_binding_validation/F3_5.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_binding_validation/F7_8.xls</t>
   </si>
   <si>
@@ -828,6 +792,42 @@
   </si>
   <si>
     <t>experimental_data/validation/BLI/oPool_binding_validation/F1_12.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_binding_validation/A2_13.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_binding_validation/B2_13.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_binding_validation/C2_13.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_binding_validation/D2_13.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_binding_validation/F3_13.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_binding_validation/E3_13.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_binding_validation/A1_13.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_binding_validation/B1_13.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_binding_validation/C1_13.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_binding_validation/D1_13.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_binding_validation/E1_13.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_binding_validation/F1_13.xls</t>
   </si>
 </sst>
 </file>
@@ -1384,7 +1384,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>53</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -1395,7 +1395,7 @@
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -1406,7 +1406,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -1417,7 +1417,7 @@
         <v>4</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -1428,7 +1428,7 @@
         <v>4</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -1439,7 +1439,7 @@
         <v>4</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -1450,7 +1450,7 @@
         <v>4</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -1461,7 +1461,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -1472,7 +1472,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -1483,7 +1483,7 @@
         <v>4</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -1494,7 +1494,7 @@
         <v>23</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E27" s="1"/>
     </row>
@@ -1506,7 +1506,7 @@
         <v>23</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E28" s="1"/>
     </row>
@@ -1518,7 +1518,7 @@
         <v>23</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E29" s="1"/>
     </row>
@@ -1530,7 +1530,7 @@
         <v>23</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E30" s="1"/>
     </row>
@@ -1542,7 +1542,7 @@
         <v>23</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E31" s="1"/>
     </row>
@@ -1554,7 +1554,7 @@
         <v>23</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E32" s="1"/>
     </row>
@@ -1566,7 +1566,7 @@
         <v>23</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E33" s="1"/>
     </row>
@@ -1578,7 +1578,7 @@
         <v>23</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E34" s="1"/>
     </row>
@@ -1590,7 +1590,7 @@
         <v>23</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E35" s="1"/>
     </row>
@@ -1602,7 +1602,7 @@
         <v>23</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E36" s="1"/>
     </row>
@@ -1614,7 +1614,7 @@
         <v>23</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E37" s="1"/>
     </row>
@@ -1626,7 +1626,7 @@
         <v>23</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E38" s="1"/>
     </row>
@@ -1638,7 +1638,7 @@
         <v>23</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E39" s="1"/>
     </row>
@@ -1650,7 +1650,7 @@
         <v>23</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E40" s="1"/>
     </row>
@@ -1662,7 +1662,7 @@
         <v>23</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E41" s="1"/>
     </row>
@@ -1674,7 +1674,7 @@
         <v>23</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E42" s="1"/>
     </row>
@@ -1686,7 +1686,7 @@
         <v>23</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E43" s="1"/>
     </row>
@@ -1698,7 +1698,7 @@
         <v>23</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E44" s="1"/>
     </row>
@@ -1710,7 +1710,7 @@
         <v>23</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E45" s="1"/>
     </row>
@@ -1722,7 +1722,7 @@
         <v>23</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E46" s="1"/>
     </row>
@@ -1734,7 +1734,7 @@
         <v>23</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E47" s="1"/>
     </row>
@@ -1746,7 +1746,7 @@
         <v>23</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E48" s="1"/>
     </row>
@@ -1758,7 +1758,7 @@
         <v>23</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
@@ -1769,7 +1769,7 @@
         <v>23</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -1780,7 +1780,7 @@
         <v>23</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
@@ -1791,7 +1791,7 @@
         <v>33</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
@@ -1802,7 +1802,7 @@
         <v>33</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -1813,7 +1813,7 @@
         <v>33</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -1824,7 +1824,7 @@
         <v>33</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
@@ -1835,7 +1835,7 @@
         <v>33</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
@@ -1846,7 +1846,7 @@
         <v>33</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
@@ -1857,7 +1857,7 @@
         <v>33</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
@@ -1868,7 +1868,7 @@
         <v>33</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
@@ -1879,7 +1879,7 @@
         <v>33</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
@@ -1890,7 +1890,7 @@
         <v>33</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
@@ -1901,7 +1901,7 @@
         <v>33</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
@@ -1912,7 +1912,7 @@
         <v>33</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
@@ -1923,7 +1923,7 @@
         <v>33</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
@@ -1934,7 +1934,7 @@
         <v>33</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -1945,7 +1945,7 @@
         <v>33</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
@@ -1956,7 +1956,7 @@
         <v>33</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
@@ -1967,7 +1967,7 @@
         <v>33</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
@@ -1978,7 +1978,7 @@
         <v>33</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
@@ -1989,7 +1989,7 @@
         <v>33</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
@@ -2000,7 +2000,7 @@
         <v>33</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
@@ -2011,7 +2011,7 @@
         <v>33</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
@@ -2022,7 +2022,7 @@
         <v>33</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
@@ -2033,7 +2033,7 @@
         <v>33</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
@@ -2044,7 +2044,7 @@
         <v>33</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
@@ -2055,7 +2055,7 @@
         <v>33</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -2066,7 +2066,7 @@
         <v>34</v>
       </c>
       <c r="C77" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
@@ -2077,7 +2077,7 @@
         <v>34</v>
       </c>
       <c r="C78" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
@@ -2088,7 +2088,7 @@
         <v>34</v>
       </c>
       <c r="C79" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
@@ -2099,7 +2099,7 @@
         <v>34</v>
       </c>
       <c r="C80" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
@@ -2110,7 +2110,7 @@
         <v>34</v>
       </c>
       <c r="C81" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
@@ -2121,7 +2121,7 @@
         <v>34</v>
       </c>
       <c r="C82" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
@@ -2132,7 +2132,7 @@
         <v>34</v>
       </c>
       <c r="C83" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
@@ -2143,7 +2143,7 @@
         <v>34</v>
       </c>
       <c r="C84" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
@@ -2154,7 +2154,7 @@
         <v>34</v>
       </c>
       <c r="C85" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
@@ -2165,7 +2165,7 @@
         <v>34</v>
       </c>
       <c r="C86" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
@@ -2176,7 +2176,7 @@
         <v>34</v>
       </c>
       <c r="C87" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
@@ -2187,7 +2187,7 @@
         <v>34</v>
       </c>
       <c r="C88" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
@@ -2198,7 +2198,7 @@
         <v>34</v>
       </c>
       <c r="C89" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
@@ -2209,7 +2209,7 @@
         <v>34</v>
       </c>
       <c r="C90" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
@@ -2220,7 +2220,7 @@
         <v>34</v>
       </c>
       <c r="C91" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
@@ -2231,7 +2231,7 @@
         <v>34</v>
       </c>
       <c r="C92" t="s">
-        <v>128</v>
+        <v>252</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
@@ -2242,7 +2242,7 @@
         <v>34</v>
       </c>
       <c r="C93" t="s">
-        <v>129</v>
+        <v>258</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
@@ -2253,7 +2253,7 @@
         <v>34</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
@@ -2264,7 +2264,7 @@
         <v>34</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
@@ -2275,7 +2275,7 @@
         <v>34</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
@@ -2286,7 +2286,7 @@
         <v>34</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
@@ -2297,7 +2297,7 @@
         <v>34</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
@@ -2308,7 +2308,7 @@
         <v>34</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
@@ -2319,7 +2319,7 @@
         <v>34</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
@@ -2330,7 +2330,7 @@
         <v>34</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
@@ -2341,7 +2341,7 @@
         <v>35</v>
       </c>
       <c r="C102" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
@@ -2352,7 +2352,7 @@
         <v>35</v>
       </c>
       <c r="C103" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
@@ -2363,7 +2363,7 @@
         <v>35</v>
       </c>
       <c r="C104" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
@@ -2374,7 +2374,7 @@
         <v>35</v>
       </c>
       <c r="C105" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
@@ -2385,7 +2385,7 @@
         <v>35</v>
       </c>
       <c r="C106" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
@@ -2396,7 +2396,7 @@
         <v>35</v>
       </c>
       <c r="C107" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
@@ -2407,7 +2407,7 @@
         <v>35</v>
       </c>
       <c r="C108" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
@@ -2418,7 +2418,7 @@
         <v>35</v>
       </c>
       <c r="C109" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
@@ -2429,7 +2429,7 @@
         <v>35</v>
       </c>
       <c r="C110" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
@@ -2440,7 +2440,7 @@
         <v>35</v>
       </c>
       <c r="C111" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
@@ -2451,7 +2451,7 @@
         <v>35</v>
       </c>
       <c r="C112" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
@@ -2462,7 +2462,7 @@
         <v>35</v>
       </c>
       <c r="C113" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
@@ -2473,7 +2473,7 @@
         <v>35</v>
       </c>
       <c r="C114" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
@@ -2484,7 +2484,7 @@
         <v>35</v>
       </c>
       <c r="C115" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
@@ -2495,7 +2495,7 @@
         <v>35</v>
       </c>
       <c r="C116" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
@@ -2506,7 +2506,7 @@
         <v>35</v>
       </c>
       <c r="C117" t="s">
-        <v>153</v>
+        <v>253</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
@@ -2517,7 +2517,7 @@
         <v>35</v>
       </c>
       <c r="C118" t="s">
-        <v>154</v>
+        <v>259</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
@@ -2528,7 +2528,7 @@
         <v>35</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
@@ -2539,7 +2539,7 @@
         <v>35</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
@@ -2550,7 +2550,7 @@
         <v>35</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
@@ -2561,7 +2561,7 @@
         <v>35</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
@@ -2572,7 +2572,7 @@
         <v>35</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
@@ -2583,7 +2583,7 @@
         <v>35</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
@@ -2594,7 +2594,7 @@
         <v>35</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
@@ -2605,7 +2605,7 @@
         <v>35</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
@@ -2616,7 +2616,7 @@
         <v>36</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
@@ -2627,7 +2627,7 @@
         <v>36</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
@@ -2638,7 +2638,7 @@
         <v>36</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
@@ -2649,7 +2649,7 @@
         <v>36</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
@@ -2660,7 +2660,7 @@
         <v>36</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
@@ -2671,7 +2671,7 @@
         <v>36</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
@@ -2682,7 +2682,7 @@
         <v>36</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
@@ -2693,7 +2693,7 @@
         <v>36</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
@@ -2704,7 +2704,7 @@
         <v>36</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
@@ -2715,7 +2715,7 @@
         <v>36</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
@@ -2726,7 +2726,7 @@
         <v>36</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
@@ -2737,7 +2737,7 @@
         <v>36</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
@@ -2748,7 +2748,7 @@
         <v>36</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
@@ -2759,7 +2759,7 @@
         <v>36</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
@@ -2770,7 +2770,7 @@
         <v>36</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
@@ -2781,7 +2781,7 @@
         <v>36</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
@@ -2792,7 +2792,7 @@
         <v>36</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
@@ -2803,7 +2803,7 @@
         <v>36</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
@@ -2814,7 +2814,7 @@
         <v>36</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.2">
@@ -2825,7 +2825,7 @@
         <v>36</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.2">
@@ -2836,7 +2836,7 @@
         <v>36</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.2">
@@ -2847,7 +2847,7 @@
         <v>36</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
@@ -2858,7 +2858,7 @@
         <v>36</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.2">
@@ -2869,7 +2869,7 @@
         <v>36</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.2">
@@ -2880,7 +2880,7 @@
         <v>36</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.2">
@@ -2891,7 +2891,7 @@
         <v>37</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
@@ -2902,7 +2902,7 @@
         <v>37</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
@@ -2913,7 +2913,7 @@
         <v>37</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
@@ -2924,7 +2924,7 @@
         <v>37</v>
       </c>
       <c r="C155" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
@@ -2935,7 +2935,7 @@
         <v>37</v>
       </c>
       <c r="C156" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.2">
@@ -2946,7 +2946,7 @@
         <v>37</v>
       </c>
       <c r="C157" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.2">
@@ -2957,7 +2957,7 @@
         <v>37</v>
       </c>
       <c r="C158" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.2">
@@ -2968,7 +2968,7 @@
         <v>37</v>
       </c>
       <c r="C159" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.2">
@@ -2979,7 +2979,7 @@
         <v>37</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.2">
@@ -2990,7 +2990,7 @@
         <v>37</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
@@ -3001,7 +3001,7 @@
         <v>37</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.2">
@@ -3012,7 +3012,7 @@
         <v>37</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
@@ -3023,7 +3023,7 @@
         <v>37</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
@@ -3034,7 +3034,7 @@
         <v>37</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
@@ -3045,7 +3045,7 @@
         <v>37</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
@@ -3056,7 +3056,7 @@
         <v>37</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>203</v>
+        <v>254</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.2">
@@ -3067,7 +3067,7 @@
         <v>37</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>204</v>
+        <v>260</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.2">
@@ -3078,7 +3078,7 @@
         <v>37</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.2">
@@ -3089,7 +3089,7 @@
         <v>37</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.2">
@@ -3100,7 +3100,7 @@
         <v>37</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.2">
@@ -3111,7 +3111,7 @@
         <v>37</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.2">
@@ -3122,7 +3122,7 @@
         <v>37</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.2">
@@ -3133,7 +3133,7 @@
         <v>37</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
@@ -3144,7 +3144,7 @@
         <v>37</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
@@ -3155,7 +3155,7 @@
         <v>37</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
@@ -3166,7 +3166,7 @@
         <v>15</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
@@ -3177,7 +3177,7 @@
         <v>15</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.2">
@@ -3188,7 +3188,7 @@
         <v>16</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.2">
@@ -3199,7 +3199,7 @@
         <v>16</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.2">
@@ -3210,7 +3210,7 @@
         <v>16</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.2">
@@ -3221,7 +3221,7 @@
         <v>16</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.2">
@@ -3232,7 +3232,7 @@
         <v>16</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
@@ -3243,7 +3243,7 @@
         <v>16</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.2">
@@ -3254,7 +3254,7 @@
         <v>16</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
@@ -3265,7 +3265,7 @@
         <v>16</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
@@ -3276,7 +3276,7 @@
         <v>16</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
@@ -3287,7 +3287,7 @@
         <v>16</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
@@ -3298,7 +3298,7 @@
         <v>16</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.2">
@@ -3309,7 +3309,7 @@
         <v>16</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.2">
@@ -3320,7 +3320,7 @@
         <v>16</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.2">
@@ -3331,7 +3331,7 @@
         <v>16</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.2">
@@ -3342,7 +3342,7 @@
         <v>16</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>229</v>
+        <v>261</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.2">
@@ -3353,7 +3353,7 @@
         <v>16</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.2">
@@ -3364,7 +3364,7 @@
         <v>16</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.2">
@@ -3375,7 +3375,7 @@
         <v>16</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
@@ -3386,7 +3386,7 @@
         <v>16</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
@@ -3397,7 +3397,7 @@
         <v>16</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
@@ -3408,7 +3408,7 @@
         <v>16</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
@@ -3419,7 +3419,7 @@
         <v>16</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.2">
@@ -3430,7 +3430,7 @@
         <v>16</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.2">
@@ -3441,7 +3441,7 @@
         <v>17</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.2">
@@ -3452,7 +3452,7 @@
         <v>17</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.2">
@@ -3463,7 +3463,7 @@
         <v>17</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.2">
@@ -3474,7 +3474,7 @@
         <v>17</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.2">
@@ -3485,7 +3485,7 @@
         <v>17</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.2">
@@ -3496,7 +3496,7 @@
         <v>17</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
@@ -3507,7 +3507,7 @@
         <v>17</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
@@ -3518,7 +3518,7 @@
         <v>17</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
@@ -3529,7 +3529,7 @@
         <v>17</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
@@ -3540,7 +3540,7 @@
         <v>17</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.2">
@@ -3551,7 +3551,7 @@
         <v>17</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.2">
@@ -3562,7 +3562,7 @@
         <v>17</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.2">
@@ -3573,7 +3573,7 @@
         <v>17</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.2">
@@ -3584,7 +3584,7 @@
         <v>17</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.2">
@@ -3595,7 +3595,7 @@
         <v>17</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.2">
@@ -3606,7 +3606,7 @@
         <v>17</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.2">
@@ -3617,7 +3617,7 @@
         <v>17</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
@@ -3628,7 +3628,7 @@
         <v>17</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
@@ -3639,7 +3639,7 @@
         <v>17</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.2">
@@ -3650,7 +3650,7 @@
         <v>17</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
@@ -3661,7 +3661,7 @@
         <v>17</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.2">
@@ -3672,7 +3672,7 @@
         <v>17</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.2">
@@ -3683,7 +3683,7 @@
         <v>17</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.2">
@@ -3694,7 +3694,7 @@
         <v>17</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.2">
@@ -3705,7 +3705,7 @@
         <v>17</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/oPool_display/experimental_data/validation/BLI/oPool_binding_validation/oPool_validation_sample_names.xlsx
+++ b/oPool_display/experimental_data/validation/BLI/oPool_binding_validation/oPool_validation_sample_names.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/owenouyang/Desktop/Git_Repo/oPool_display/oPool_display/experimental_data/validation/BLI/oPool_binding_validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E106B239-1404-C84E-AEFA-296633B5C222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4EA824-708F-0D4D-911E-D3DA0B50DD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="35800" yWindow="500" windowWidth="28040" windowHeight="17440" xr2:uid="{AA0690F2-11C0-B342-945D-36AF2DF8266B}"/>
   </bookViews>
@@ -116,9 +116,6 @@
     <t>C7-3-C02</t>
   </si>
   <si>
-    <t>C3-2-F02</t>
-  </si>
-  <si>
     <t>3C11</t>
   </si>
   <si>
@@ -828,6 +825,9 @@
   </si>
   <si>
     <t>experimental_data/validation/BLI/oPool_binding_validation/F1_13.xls</t>
+  </si>
+  <si>
+    <t>C3-2-3F02</t>
   </si>
 </sst>
 </file>
@@ -1193,6 +1193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14F7587E-F2F5-0241-BB45-F101F20DEA3C}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E226"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1211,7 +1212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1219,10 +1220,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1230,10 +1231,10 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1241,21 +1242,21 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>262</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1263,10 +1264,10 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1274,10 +1275,10 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1285,10 +1286,10 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1296,10 +1297,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1307,10 +1308,10 @@
         <v>4</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1318,54 +1319,54 @@
         <v>4</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -1373,10 +1374,10 @@
         <v>4</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1384,10 +1385,10 @@
         <v>4</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1395,10 +1396,10 @@
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -1406,10 +1407,10 @@
         <v>4</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -1417,10 +1418,10 @@
         <v>4</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -1428,10 +1429,10 @@
         <v>4</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -1439,10 +1440,10 @@
         <v>4</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -1450,43 +1451,43 @@
         <v>4</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
         <v>4</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B25" t="s">
         <v>4</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
         <v>4</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1494,11 +1495,11 @@
         <v>23</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -1506,11 +1507,11 @@
         <v>23</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -1518,23 +1519,23 @@
         <v>23</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E29" s="1"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>262</v>
       </c>
       <c r="B30" t="s">
         <v>23</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -1542,11 +1543,11 @@
         <v>23</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>8</v>
       </c>
@@ -1554,11 +1555,11 @@
         <v>23</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>9</v>
       </c>
@@ -1566,11 +1567,11 @@
         <v>23</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -1578,11 +1579,11 @@
         <v>23</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -1590,11 +1591,11 @@
         <v>23</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -1602,59 +1603,59 @@
         <v>23</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B37" t="s">
         <v>23</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B38" t="s">
         <v>23</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B39" t="s">
         <v>23</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B40" t="s">
         <v>23</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E40" s="1"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>13</v>
       </c>
@@ -1662,11 +1663,11 @@
         <v>23</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E41" s="1"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>14</v>
       </c>
@@ -1674,11 +1675,11 @@
         <v>23</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E42" s="1"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>24</v>
       </c>
@@ -1686,11 +1687,11 @@
         <v>23</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E43" s="1"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>18</v>
       </c>
@@ -1698,11 +1699,11 @@
         <v>23</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E44" s="1"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>19</v>
       </c>
@@ -1710,11 +1711,11 @@
         <v>23</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E45" s="1"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>20</v>
       </c>
@@ -1722,11 +1723,11 @@
         <v>23</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E46" s="1"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>21</v>
       </c>
@@ -1734,11 +1735,11 @@
         <v>23</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E47" s="1"/>
     </row>
-    <row r="48" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>22</v>
       </c>
@@ -1746,1419 +1747,1419 @@
         <v>23</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E48" s="1"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B49" t="s">
         <v>23</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B50" t="s">
         <v>23</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B51" t="s">
         <v>23</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>5</v>
       </c>
       <c r="B53" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>6</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>25</v>
+        <v>262</v>
       </c>
       <c r="B55" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>7</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>9</v>
       </c>
       <c r="B58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>10</v>
       </c>
       <c r="B59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C61" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>31</v>
+      </c>
+      <c r="B62" t="s">
+        <v>32</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
+    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>30</v>
+      </c>
+      <c r="B63" t="s">
         <v>32</v>
       </c>
-      <c r="B62" t="s">
-        <v>33</v>
-      </c>
-      <c r="C62" s="1" t="s">
+      <c r="C63" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>31</v>
-      </c>
-      <c r="B63" t="s">
-        <v>33</v>
-      </c>
-      <c r="C63" s="1" t="s">
+    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>29</v>
+      </c>
+      <c r="B64" t="s">
+        <v>32</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>30</v>
-      </c>
-      <c r="B64" t="s">
-        <v>33</v>
-      </c>
-      <c r="C64" s="1" t="s">
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>28</v>
+      </c>
+      <c r="B65" t="s">
+        <v>32</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>29</v>
-      </c>
-      <c r="B65" t="s">
-        <v>33</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>13</v>
       </c>
       <c r="B66" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B68" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B69" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B70" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B71" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B72" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B73" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C73" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B74" t="s">
+        <v>32</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
+    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B74" t="s">
-        <v>33</v>
-      </c>
-      <c r="C74" s="1" t="s">
+      <c r="B75" t="s">
+        <v>32</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
+    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B75" t="s">
-        <v>33</v>
-      </c>
-      <c r="C75" s="1" t="s">
+      <c r="B76" t="s">
+        <v>32</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A76" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B76" t="s">
-        <v>33</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>3</v>
       </c>
       <c r="B77" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C77" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>5</v>
       </c>
       <c r="B78" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C78" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>6</v>
       </c>
       <c r="B79" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C79" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>25</v>
+        <v>262</v>
       </c>
       <c r="B80" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C80" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>7</v>
       </c>
       <c r="B81" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C81" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C82" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>9</v>
       </c>
       <c r="B83" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C83" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>10</v>
       </c>
       <c r="B84" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C84" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>11</v>
       </c>
       <c r="B85" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C85" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C86" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>31</v>
+      </c>
+      <c r="B87" t="s">
+        <v>33</v>
+      </c>
+      <c r="C87" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
-        <v>32</v>
-      </c>
-      <c r="B87" t="s">
-        <v>34</v>
-      </c>
-      <c r="C87" t="s">
+    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>30</v>
+      </c>
+      <c r="B88" t="s">
+        <v>33</v>
+      </c>
+      <c r="C88" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
-        <v>31</v>
-      </c>
-      <c r="B88" t="s">
-        <v>34</v>
-      </c>
-      <c r="C88" t="s">
+    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>29</v>
+      </c>
+      <c r="B89" t="s">
+        <v>33</v>
+      </c>
+      <c r="C89" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
-        <v>30</v>
-      </c>
-      <c r="B89" t="s">
-        <v>34</v>
-      </c>
-      <c r="C89" t="s">
+    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>28</v>
+      </c>
+      <c r="B90" t="s">
+        <v>33</v>
+      </c>
+      <c r="C90" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
-        <v>29</v>
-      </c>
-      <c r="B90" t="s">
-        <v>34</v>
-      </c>
-      <c r="C90" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C91" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>14</v>
       </c>
       <c r="B92" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C92" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B93" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C93" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B94" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B95" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B96" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B97" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B98" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C98" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B99" t="s">
+        <v>33</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A99" s="1" t="s">
+    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B99" t="s">
-        <v>34</v>
-      </c>
-      <c r="C99" s="1" t="s">
+      <c r="B100" t="s">
+        <v>33</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A100" s="1" t="s">
+    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B100" t="s">
-        <v>34</v>
-      </c>
-      <c r="C100" s="1" t="s">
+      <c r="B101" t="s">
+        <v>33</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A101" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B101" t="s">
-        <v>34</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>3</v>
       </c>
       <c r="B102" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C102" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>5</v>
       </c>
       <c r="B103" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C103" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>6</v>
       </c>
       <c r="B104" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C104" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>25</v>
+        <v>262</v>
       </c>
       <c r="B105" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C105" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>7</v>
       </c>
       <c r="B106" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C106" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C107" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>9</v>
       </c>
       <c r="B108" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C108" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>10</v>
       </c>
       <c r="B109" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C109" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>11</v>
       </c>
       <c r="B110" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C110" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C111" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>31</v>
+      </c>
+      <c r="B112" t="s">
+        <v>34</v>
+      </c>
+      <c r="C112" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
-        <v>32</v>
-      </c>
-      <c r="B112" t="s">
-        <v>35</v>
-      </c>
-      <c r="C112" t="s">
+    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>30</v>
+      </c>
+      <c r="B113" t="s">
+        <v>34</v>
+      </c>
+      <c r="C113" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A113" t="s">
-        <v>31</v>
-      </c>
-      <c r="B113" t="s">
-        <v>35</v>
-      </c>
-      <c r="C113" t="s">
+    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>29</v>
+      </c>
+      <c r="B114" t="s">
+        <v>34</v>
+      </c>
+      <c r="C114" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
-        <v>30</v>
-      </c>
-      <c r="B114" t="s">
-        <v>35</v>
-      </c>
-      <c r="C114" t="s">
+    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>28</v>
+      </c>
+      <c r="B115" t="s">
+        <v>34</v>
+      </c>
+      <c r="C115" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
-        <v>29</v>
-      </c>
-      <c r="B115" t="s">
-        <v>35</v>
-      </c>
-      <c r="C115" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>13</v>
       </c>
       <c r="B116" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C116" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>14</v>
       </c>
       <c r="B117" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C117" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B118" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B119" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B120" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B121" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B122" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B123" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C123" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B124" t="s">
+        <v>34</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A124" s="1" t="s">
+    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B124" t="s">
-        <v>35</v>
-      </c>
-      <c r="C124" s="1" t="s">
+      <c r="B125" t="s">
+        <v>34</v>
+      </c>
+      <c r="C125" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A125" s="1" t="s">
+    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B125" t="s">
-        <v>35</v>
-      </c>
-      <c r="C125" s="1" t="s">
+      <c r="B126" t="s">
+        <v>34</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A126" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B126" t="s">
-        <v>35</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B127" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B128" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B129" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>25</v>
+        <v>262</v>
       </c>
       <c r="B130" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B131" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B133" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B134" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B135" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B136" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C136" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B137" t="s">
+        <v>35</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A137" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B137" t="s">
-        <v>36</v>
-      </c>
-      <c r="C137" s="1" t="s">
+    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B138" t="s">
+        <v>35</v>
+      </c>
+      <c r="C138" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A138" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B138" t="s">
-        <v>36</v>
-      </c>
-      <c r="C138" s="1" t="s">
+    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B139" t="s">
+        <v>35</v>
+      </c>
+      <c r="C139" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A139" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B139" t="s">
-        <v>36</v>
-      </c>
-      <c r="C139" s="1" t="s">
+    <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B140" t="s">
+        <v>35</v>
+      </c>
+      <c r="C140" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A140" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B140" t="s">
-        <v>36</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B141" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B142" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B143" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B144" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B145" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B146" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B147" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B148" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C148" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B149" t="s">
+        <v>35</v>
+      </c>
+      <c r="C149" s="1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A149" s="1" t="s">
+    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B149" t="s">
-        <v>36</v>
-      </c>
-      <c r="C149" s="1" t="s">
+      <c r="B150" t="s">
+        <v>35</v>
+      </c>
+      <c r="C150" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A150" s="1" t="s">
+    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B150" t="s">
-        <v>36</v>
-      </c>
-      <c r="C150" s="1" t="s">
+      <c r="B151" t="s">
+        <v>35</v>
+      </c>
+      <c r="C151" s="1" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A151" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B151" t="s">
-        <v>36</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>3</v>
       </c>
       <c r="B152" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>5</v>
       </c>
       <c r="B153" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>6</v>
       </c>
       <c r="B154" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>25</v>
+        <v>262</v>
       </c>
       <c r="B155" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C155" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>7</v>
       </c>
       <c r="B156" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C156" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>8</v>
       </c>
       <c r="B157" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C157" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>9</v>
       </c>
       <c r="B158" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C158" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>10</v>
       </c>
       <c r="B159" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C159" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>11</v>
       </c>
       <c r="B160" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C161" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>31</v>
+      </c>
+      <c r="B162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C162" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A162" t="s">
-        <v>32</v>
-      </c>
-      <c r="B162" t="s">
-        <v>37</v>
-      </c>
-      <c r="C162" s="1" t="s">
+    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>30</v>
+      </c>
+      <c r="B163" t="s">
+        <v>36</v>
+      </c>
+      <c r="C163" s="1" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A163" t="s">
-        <v>31</v>
-      </c>
-      <c r="B163" t="s">
-        <v>37</v>
-      </c>
-      <c r="C163" s="1" t="s">
+    <row r="164" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>29</v>
+      </c>
+      <c r="B164" t="s">
+        <v>36</v>
+      </c>
+      <c r="C164" s="1" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A164" t="s">
-        <v>30</v>
-      </c>
-      <c r="B164" t="s">
-        <v>37</v>
-      </c>
-      <c r="C164" s="1" t="s">
+    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>28</v>
+      </c>
+      <c r="B165" t="s">
+        <v>36</v>
+      </c>
+      <c r="C165" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A165" t="s">
-        <v>29</v>
-      </c>
-      <c r="B165" t="s">
-        <v>37</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>13</v>
       </c>
       <c r="B166" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>14</v>
       </c>
       <c r="B167" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B168" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B169" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B170" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B171" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B172" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B173" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C173" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A174" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B174" t="s">
+        <v>36</v>
+      </c>
+      <c r="C174" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A174" s="1" t="s">
+    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B174" t="s">
-        <v>37</v>
-      </c>
-      <c r="C174" s="1" t="s">
+      <c r="B175" t="s">
+        <v>36</v>
+      </c>
+      <c r="C175" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A175" s="1" t="s">
+    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B175" t="s">
-        <v>37</v>
-      </c>
-      <c r="C175" s="1" t="s">
+      <c r="B176" t="s">
+        <v>36</v>
+      </c>
+      <c r="C176" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A176" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B176" t="s">
-        <v>37</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>3</v>
       </c>
@@ -3166,10 +3167,10 @@
         <v>15</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>5</v>
       </c>
@@ -3177,10 +3178,10 @@
         <v>15</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>6</v>
       </c>
@@ -3188,21 +3189,21 @@
         <v>16</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>25</v>
+        <v>262</v>
       </c>
       <c r="B180" t="s">
         <v>16</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>7</v>
       </c>
@@ -3210,10 +3211,10 @@
         <v>16</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>8</v>
       </c>
@@ -3221,10 +3222,10 @@
         <v>16</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>9</v>
       </c>
@@ -3232,10 +3233,10 @@
         <v>16</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>10</v>
       </c>
@@ -3243,10 +3244,10 @@
         <v>16</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>11</v>
       </c>
@@ -3254,10 +3255,10 @@
         <v>16</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>12</v>
       </c>
@@ -3265,54 +3266,54 @@
         <v>16</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B187" t="s">
         <v>16</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B188" t="s">
         <v>16</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B189" t="s">
         <v>16</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B190" t="s">
         <v>16</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>13</v>
       </c>
@@ -3320,10 +3321,10 @@
         <v>16</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>14</v>
       </c>
@@ -3331,10 +3332,10 @@
         <v>16</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
         <v>24</v>
       </c>
@@ -3342,10 +3343,10 @@
         <v>16</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
         <v>18</v>
       </c>
@@ -3353,10 +3354,10 @@
         <v>16</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
         <v>19</v>
       </c>
@@ -3364,10 +3365,10 @@
         <v>16</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
         <v>20</v>
       </c>
@@ -3375,10 +3376,10 @@
         <v>16</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
         <v>21</v>
       </c>
@@ -3386,10 +3387,10 @@
         <v>16</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
         <v>22</v>
       </c>
@@ -3397,43 +3398,43 @@
         <v>16</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B199" t="s">
         <v>16</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B200" t="s">
         <v>16</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B201" t="s">
         <v>16</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>3</v>
       </c>
@@ -3441,10 +3442,10 @@
         <v>17</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>5</v>
       </c>
@@ -3452,10 +3453,10 @@
         <v>17</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>6</v>
       </c>
@@ -3463,21 +3464,21 @@
         <v>17</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>25</v>
+        <v>262</v>
       </c>
       <c r="B205" t="s">
         <v>17</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>7</v>
       </c>
@@ -3485,10 +3486,10 @@
         <v>17</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>8</v>
       </c>
@@ -3496,10 +3497,10 @@
         <v>17</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>9</v>
       </c>
@@ -3507,10 +3508,10 @@
         <v>17</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>10</v>
       </c>
@@ -3518,10 +3519,10 @@
         <v>17</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>11</v>
       </c>
@@ -3529,10 +3530,10 @@
         <v>17</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>12</v>
       </c>
@@ -3540,54 +3541,54 @@
         <v>17</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B212" t="s">
         <v>17</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B213" t="s">
         <v>17</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B214" t="s">
         <v>17</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B215" t="s">
         <v>17</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>13</v>
       </c>
@@ -3595,10 +3596,10 @@
         <v>17</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>14</v>
       </c>
@@ -3606,10 +3607,10 @@
         <v>17</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
         <v>24</v>
       </c>
@@ -3617,10 +3618,10 @@
         <v>17</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
         <v>18</v>
       </c>
@@ -3628,10 +3629,10 @@
         <v>17</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
         <v>19</v>
       </c>
@@ -3639,10 +3640,10 @@
         <v>17</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
         <v>20</v>
       </c>
@@ -3650,10 +3651,10 @@
         <v>17</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
         <v>21</v>
       </c>
@@ -3661,10 +3662,10 @@
         <v>17</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
         <v>22</v>
       </c>
@@ -3672,44 +3673,50 @@
         <v>17</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B224" t="s">
         <v>17</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B225" t="s">
         <v>17</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B226" t="s">
         <v>17</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C226" xr:uid="{14F7587E-F2F5-0241-BB45-F101F20DEA3C}"/>
+  <autoFilter ref="A1:C226" xr:uid="{14F7587E-F2F5-0241-BB45-F101F20DEA3C}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="C3-2-F02"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
